--- a/BQMP_Schedule_Jul-Aug2569.xlsx
+++ b/BQMP_Schedule_Jul-Aug2569.xlsx
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -208,11 +208,55 @@
         <color rgb="00dddddd"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00dddddd"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00dddddd"/>
+      </right>
+      <top style="thin">
+        <color rgb="00dddddd"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00dddddd"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00dddddd"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00dddddd"/>
+      </right>
+      <top style="thin">
+        <color rgb="00dddddd"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00dddddd"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -325,6 +369,8 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -740,7 +786,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>F=Full day  |  M=เช้า  |  A=บ่าย  |  OFF=หยุด  |  AL=พักร้อน  |  SL=ลาป่วย  |  PL=ลากิจ  |  PT=ชั่วโมง</t>
+          <t>F=Full day  |  S=เสาร์/หยุดฯ (09-15)  |  M=เช้า  |  A=บ่าย  |  OFF=หยุด  |  AL=พักร้อน  |  SL=ลาป่วย  |  PL=ลากิจ  |  PT=ชั่วโมง</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1695,7 @@
       </c>
       <c r="J8" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K8" s="10" t="inlineStr">
@@ -1719,7 +1765,7 @@
       </c>
       <c r="X8" s="15" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>S</t>
         </is>
       </c>
       <c r="Y8" s="10" t="inlineStr">
@@ -2019,7 +2065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2120,192 +2166,192 @@
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
+          <t>Full day (จ-ศ)</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>SND จ–ศ — OT นับถ้าเกิน 15 นาทีหลัง 18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Sat / PHoliday</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>SND เสาร์ + วันหยุดนักขัตฤกษ์ — OT นับถ้าเกิน 15 นาทีหลัง 15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
           <t>Full day</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E4" s="26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F4" s="26" t="inlineStr">
-        <is>
-          <t>SND</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>SND — OT นับถ้าเกิน 15 นาทีหลัง 18:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>Full day</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F5" s="28" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>KCN</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>KCN — OT นับถ้าเกิน 15 นาทีหลัง 20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Morning</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
-        <is>
-          <t>NVP</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>ไม่มี OT แม้ทำเกิน 19:00</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Morning</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>NVP</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>ไม่มี OT แม้ทำเกิน 19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Afternoon</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>NVP</t>
         </is>
       </c>
-      <c r="G7" s="24" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>ไม่มี OT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>วันหยุด</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="30" t="inlineStr">
-        <is>
-          <t>ทุกสาขา</t>
-        </is>
-      </c>
-      <c r="G8" s="30" t="inlineStr">
-        <is>
-          <t>ไม่นับ incident</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>ลาพักร้อน</t>
+          <t>วันหยุด</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -2330,19 +2376,19 @@
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>6วัน/ปี — หัก AL balance</t>
+          <t>ไม่นับ incident</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>ลาป่วย</t>
+          <t>ลาพักร้อน</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
@@ -2367,19 +2413,19 @@
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
-          <t>30วัน/ปี — ≥2วันติดต้องมีใบ</t>
+          <t>6วัน/ปี — หัก AL balance</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>ลากิจ</t>
+          <t>ลาป่วย</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
@@ -2404,79 +2450,116 @@
       </c>
       <c r="G11" s="30" t="inlineStr">
         <is>
-          <t>3วัน/ปี</t>
+          <t>30วัน/ปี — ≥2วันติดต้องมีใบ</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="29" t="inlineStr">
         <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>ลากิจ</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="30" t="inlineStr">
+        <is>
+          <t>ทุกสาขา</t>
+        </is>
+      </c>
+      <c r="G12" s="30" t="inlineStr">
+        <is>
+          <t>3วัน/ปี</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
           <t>LWP</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>ลาไม่รับค่า</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="30" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="30" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>ทุกสาขา</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t>เกินสิทธิ์ AL/PL</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>Part-time</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t>ยืดหยุ่น</t>
         </is>
       </c>
-      <c r="D13" s="26" t="inlineStr">
+      <c r="D14" s="26" t="inlineStr">
         <is>
           <t>ยืดหยุ่น</t>
         </is>
       </c>
-      <c r="E13" s="26" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="F13" s="26" t="inlineStr">
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>SND (Prince)</t>
         </is>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t>นับเป็นชั่วโมง 50บ/ชม. จ่ายทุกอังคาร</t>
         </is>
@@ -2496,7 +2579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2713,7 +2796,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>ot_snd_end_time</t>
+          <t>ot_snd_end_time_weekday</t>
         </is>
       </c>
       <c r="B11" s="32" t="inlineStr">
@@ -2723,7 +2806,7 @@
       </c>
       <c r="C11" s="32" t="inlineStr">
         <is>
-          <t>เวลาเลิกงาน SND</t>
+          <t>เวลาเลิกงาน SND จ–ศ</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -2735,115 +2818,127 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="33" t="inlineStr">
         <is>
-          <t>ot_kcn_min_minutes</t>
+          <t>ot_snd_end_time_sat</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>เกิน 15 นาทีถึงนับ</t>
+          <t>เวลาเลิกงาน SND เสาร์+วันหยุดฯ</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>KCN</t>
+          <t>SND</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>ot_kcn_end_time</t>
+          <t>snd_sat_shift_start</t>
         </is>
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>เวลาเลิกงาน KCN</t>
+          <t>เริ่มกะเสาร์+วันหยุดฯ</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
         <is>
-          <t>KCN</t>
+          <t>SND</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="33" t="inlineStr">
         <is>
-          <t>incident_no_scan</t>
+          <t>snd_sat_shift_end</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>ไม่สแกนทั้ง in และ out = 2 incidents</t>
-        </is>
-      </c>
-      <c r="D14" s="30" t="inlineStr"/>
+          <t>เลิกกะเสาร์+วันหยุดฯ</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>SND</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>incident_half_scan</t>
+          <t>ot_kcn_min_minutes</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
-          <t>สแกนแค่ in หรือแค่ out = 1 incident</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr"/>
+          <t>เกิน 15 นาทีถึงนับ</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>KCN</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="33" t="inlineStr">
         <is>
-          <t>incident_formula</t>
+          <t>ot_kcn_end_time</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>floor(incidents/5)*(base/60)</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>บาทที่หัก</t>
-        </is>
-      </c>
-      <c r="D16" s="30" t="inlineStr"/>
+          <t>เวลาเลิกงาน KCN</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>KCN</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>soc_sec_rate</t>
+          <t>incident_no_scan</t>
         </is>
       </c>
       <c r="B17" s="32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
         <is>
-          <t>5% ของ base</t>
+          <t>ไม่สแกนทั้ง in และ out = 2 incidents</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr"/>
@@ -2851,61 +2946,53 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="33" t="inlineStr">
         <is>
-          <t>soc_sec_cap</t>
+          <t>incident_half_scan</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>สูงสุด 820 บาท</t>
-        </is>
-      </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>min(base*5%, 820)</t>
-        </is>
-      </c>
+          <t>สแกนแค่ in หรือแค่ out = 1 incident</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>pt_rate_per_hour</t>
+          <t>incident_formula</t>
         </is>
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>floor(incidents/5)*(base/60)</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
         <is>
-          <t>บาท/ชั่วโมง</t>
-        </is>
-      </c>
-      <c r="D19" s="32" t="inlineStr">
-        <is>
-          <t>Prince เท่านั้น</t>
-        </is>
-      </c>
+          <t>บาทที่หัก</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="33" t="inlineStr">
         <is>
-          <t>pt_pay_day</t>
+          <t>soc_sec_rate</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>จ่ายทุกอังคาร</t>
+          <t>5% ของ base</t>
         </is>
       </c>
       <c r="D20" s="30" t="inlineStr"/>
@@ -2913,53 +3000,61 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>al_days_per_year</t>
+          <t>soc_sec_cap</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>820</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>วันพักร้อน/ปี</t>
-        </is>
-      </c>
-      <c r="D21" s="32" t="inlineStr"/>
+          <t>สูงสุด 820 บาท</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>min(base*5%, 820)</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="33" t="inlineStr">
         <is>
-          <t>sl_days_per_year</t>
+          <t>pt_rate_per_hour</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>วันลาป่วย/ปี</t>
-        </is>
-      </c>
-      <c r="D22" s="30" t="inlineStr"/>
+          <t>บาท/ชั่วโมง</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Prince เท่านั้น</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>pl_days_per_year</t>
+          <t>pt_pay_day</t>
         </is>
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>วันลากิจ/ปี</t>
+          <t>จ่ายทุกอังคาร</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr"/>
@@ -2967,20 +3062,74 @@
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="33" t="inlineStr">
         <is>
+          <t>al_days_per_year</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>วันพักร้อน/ปี</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>sl_days_per_year</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>วันลาป่วย/ปี</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>pl_days_per_year</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>วันลากิจ/ปี</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
           <t>leave_overflow_order</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>AL&gt;PL&gt;LWP</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>ลาเกินสิทธิ์ใช้ AL ก่อน</t>
         </is>
       </c>
-      <c r="D24" s="30" t="inlineStr"/>
+      <c r="D27" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3188,7 +3337,7 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>OT</t>
+          <t>OT จ–ศ</t>
         </is>
       </c>
       <c r="C9" s="26" t="inlineStr">
@@ -3220,25 +3369,29 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>ปิดอาทิตย์</t>
+          <t>OT เสาร์/หยุดฯ</t>
         </is>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>S shift</t>
         </is>
       </c>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>ไม่มีกะอาทิตย์</t>
+          <t>ทำเกิน 15:00 และ &gt; 15 นาที</t>
         </is>
       </c>
       <c r="E10" s="26" t="inlineStr">
         <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr"/>
+          <t>base ÷ 18,000 × 1.5 / นาที</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>กะสั้น 09:00–15:00</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -3248,29 +3401,25 @@
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>เสาร์</t>
+          <t>ปิดอาทิตย์</t>
         </is>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
-          <t>F (ครึ่งวัน)</t>
+          <t>–</t>
         </is>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
-          <t>Yam: เสาร์เว้นเสาร์</t>
+          <t>ไม่มีกะอาทิตย์</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
         <is>
-          <t>ปกติ</t>
-        </is>
-      </c>
-      <c r="F11" s="26" t="inlineStr">
-        <is>
-          <t>สลับ on/off ดูตาราง</t>
-        </is>
-      </c>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="14" t="inlineStr">
@@ -3280,27 +3429,27 @@
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>Prince PT</t>
+          <t>เสาร์</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>S (09:00–15:00)</t>
         </is>
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>นับชั่วโมงจริง</t>
+          <t>Yam: เสาร์เว้นเสาร์</t>
         </is>
       </c>
       <c r="E12" s="26" t="inlineStr">
         <is>
-          <t>50 บาท/ชม.</t>
+          <t>ปกติ</t>
         </is>
       </c>
       <c r="F12" s="26" t="inlineStr">
         <is>
-          <t>จ่ายทุกอังคาร</t>
+          <t>สลับ on/off ดูตาราง</t>
         </is>
       </c>
     </row>
@@ -3310,6 +3459,11 @@
           <t>KCN (YC + Staple)</t>
         </is>
       </c>
+      <c r="B13" s="38" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="39" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="35" t="inlineStr"/>

--- a/BQMP_Schedule_Jul-Aug2569.xlsx
+++ b/BQMP_Schedule_Jul-Aug2569.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +107,36 @@
       <color rgb="001a1a1a"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Noto Sans Thai"/>
+      <color rgb="00997700"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Noto Sans Thai"/>
+      <b val="1"/>
+      <color rgb="00997700"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Noto Sans Thai"/>
+      <b val="1"/>
+      <color rgb="003949ab"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Noto Sans Thai"/>
+      <b val="1"/>
+      <color rgb="003949ab"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans Thai"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +213,21 @@
         <fgColor rgb="00F28C35"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fff3cd"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e8f5e9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00e8eaf6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -256,7 +299,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -371,6 +414,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -786,7 +847,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>F=Full day  |  S=เสาร์/หยุดฯ (09-15)  |  M=เช้า  |  A=บ่าย  |  OFF=หยุด  |  AL=พักร้อน  |  SL=ลาป่วย  |  PL=ลากิจ  |  PT=ชั่วโมง</t>
+          <t>F=Full day  |  S=เสาร์/หยุดนักขัตฤกษ์ (09-15)  |  CO=หยุดประจำปีบริษัท  |  M=เช้า  |  A=บ่าย  |  OFF=หยุด  |  AL=พักร้อน  |  SL=ลาป่วย  |  PL=ลากิจ  |  PT=ชั่วโมง</t>
         </is>
       </c>
     </row>
@@ -807,12 +868,12 @@
           <t>26 ก.ค.</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="43" t="inlineStr">
         <is>
           <t>27 ก.ค.</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="43" t="inlineStr">
         <is>
           <t>28 ก.ค.</t>
         </is>
@@ -887,7 +948,7 @@
           <t>11 ส.ค.</t>
         </is>
       </c>
-      <c r="U3" s="5" t="inlineStr">
+      <c r="U3" s="40" t="inlineStr">
         <is>
           <t>12 ส.ค.</t>
         </is>
@@ -972,89 +1033,89 @@
           <t>อา</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>หยุดฯ</t>
+        </is>
+      </c>
+      <c r="F4" s="43" t="inlineStr">
+        <is>
+          <t>หยุดฯ</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>พ</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>พฤ</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>ศ</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>ส</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>อา</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>จ</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>อ</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>พ</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>พฤ</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>ศ</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>ส</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>อา</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>จ</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>อ</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>พ</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>พฤ</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>ศ</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>ส</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>อา</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>จ</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr">
-        <is>
-          <t>อ</t>
-        </is>
-      </c>
-      <c r="U4" s="5" t="inlineStr">
-        <is>
-          <t>พ</t>
+      <c r="U4" s="40" t="inlineStr">
+        <is>
+          <t>หยุด</t>
         </is>
       </c>
       <c r="V4" s="5" t="inlineStr">
@@ -1143,14 +1204,14 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>OFF</t>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F5" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -1318,14 +1379,14 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
@@ -1493,14 +1554,14 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -1668,14 +1729,14 @@
           <t>ปิด</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
@@ -1693,7 +1754,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="J8" s="15" t="inlineStr">
+      <c r="J8" s="42" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1748,9 +1809,9 @@
           <t>F</t>
         </is>
       </c>
-      <c r="U8" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="U8" s="42" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
       <c r="V8" s="9" t="inlineStr">
@@ -1763,7 +1824,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="X8" s="15" t="inlineStr">
+      <c r="X8" s="42" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1838,37 +1899,161 @@
           <t>PT</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="17" t="inlineStr"/>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-      <c r="I9" s="17" t="inlineStr"/>
-      <c r="J9" s="17" t="inlineStr"/>
-      <c r="K9" s="17" t="inlineStr"/>
-      <c r="L9" s="17" t="inlineStr"/>
-      <c r="M9" s="17" t="inlineStr"/>
-      <c r="N9" s="17" t="inlineStr"/>
-      <c r="O9" s="17" t="inlineStr"/>
-      <c r="P9" s="17" t="inlineStr"/>
-      <c r="Q9" s="17" t="inlineStr"/>
-      <c r="R9" s="17" t="inlineStr"/>
-      <c r="S9" s="17" t="inlineStr"/>
-      <c r="T9" s="17" t="inlineStr"/>
-      <c r="U9" s="17" t="inlineStr"/>
-      <c r="V9" s="17" t="inlineStr"/>
-      <c r="W9" s="17" t="inlineStr"/>
-      <c r="X9" s="17" t="inlineStr"/>
-      <c r="Y9" s="17" t="inlineStr"/>
-      <c r="Z9" s="17" t="inlineStr"/>
-      <c r="AA9" s="17" t="inlineStr"/>
-      <c r="AB9" s="17" t="inlineStr"/>
-      <c r="AC9" s="17" t="inlineStr"/>
-      <c r="AD9" s="17" t="inlineStr"/>
-      <c r="AE9" s="17" t="inlineStr"/>
-      <c r="AF9" s="17" t="inlineStr"/>
-      <c r="AG9" s="17" t="inlineStr"/>
-      <c r="AH9" s="17" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>ปิด</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>ปิด</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Q9" s="42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>ปิด</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="X9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y9" s="10" t="inlineStr">
+        <is>
+          <t>ปิด</t>
+        </is>
+      </c>
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AB9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AC9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AE9" s="42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AF9" s="10" t="inlineStr">
+        <is>
+          <t>ปิด</t>
+        </is>
+      </c>
+      <c r="AG9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH9" s="9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="AI9" s="16" t="inlineStr">
         <is>
           <t>PT 50บ/ชม. — กรอกจำนวนชม.</t>
@@ -1894,14 +2079,14 @@
           <t>F</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>F</t>
+      <c r="E10" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>CO</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -2083,6 +2268,12 @@
           <t>BQMP — นิยามกะ (Shift Definitions)</t>
         </is>
       </c>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="38" t="n"/>
+      <c r="F1" s="38" t="n"/>
+      <c r="G1" s="39" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2579,7 +2770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2594,6 +2785,9 @@
           <t>BQMP — Payroll Rules (สำหรับ script อ่าน)</t>
         </is>
       </c>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="39" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -3130,6 +3324,28 @@
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>company_holiday_code</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C28" s="45" t="inlineStr">
+        <is>
+          <t>วันหยุดประจำปีของบริษัท — ไม่หักจาก AL/PL</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="inlineStr">
+        <is>
+          <t>จ่ายเต็มวัน</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3162,6 +3378,11 @@
           <t>เงื่อนไข OT + สาย แยกตามสาขา</t>
         </is>
       </c>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="38" t="n"/>
+      <c r="F1" s="39" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="34" t="inlineStr">
@@ -3169,6 +3390,11 @@
           <t>NVP</t>
         </is>
       </c>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="39" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="35" t="inlineStr"/>
@@ -3300,6 +3526,11 @@
           <t>SND</t>
         </is>
       </c>
+      <c r="B7" s="38" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="38" t="n"/>
+      <c r="E7" s="38" t="n"/>
+      <c r="F7" s="39" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="35" t="inlineStr"/>
